--- a/患者満足度アンケート集計表.xlsx
+++ b/患者満足度アンケート集計表.xlsx
@@ -7,7 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="患者満足度アンケート集計" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="4月" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="5月" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="6月" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="7月" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="8月" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="9月" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="10月" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="11月" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="12月" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="1月" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2月" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="3月" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -503,12 +514,12 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>患者満足度アンケート集計表</t>
+          <t>患者満足度アンケート集計表（4月）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>回収率：60%</t>
+          <t>回収率：</t>
         </is>
       </c>
     </row>
@@ -1259,4 +1270,8870 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>患者満足度アンケート集計表（1月）</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>回収率：</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>患者</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年代</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>看護師の対応で気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
+      <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8">
+        <f>SUM(C7:AG7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8">
+        <f>SUM(C8:AG8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>看護師の服装や身だしなみで気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="8" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8">
+        <f>SUM(C10:AG10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
+      <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8">
+        <f>SUM(C11:AG11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ナースコールは迅速に対応できましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
+      <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8">
+        <f>SUM(C13:AG13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8">
+        <f>SUM(C14:AG14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>病室内の環境で不快な点はありましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="8" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8">
+        <f>SUM(C16:AG16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="8" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="8" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
+      <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8">
+        <f>SUM(C17:AG17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>病室内は整理整頓されていましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="8" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="8" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
+      <c r="AE19" s="8" t="n"/>
+      <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8">
+        <f>SUM(C19:AG19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="8" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="8" t="n"/>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="8" t="n"/>
+      <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8">
+        <f>SUM(C20:AG20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>自由記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B23:AH25"/>
+    <mergeCell ref="B18:AH18"/>
+    <mergeCell ref="B9:AH9"/>
+    <mergeCell ref="B26:AH28"/>
+    <mergeCell ref="B12:AH12"/>
+    <mergeCell ref="B35:AH37"/>
+    <mergeCell ref="B6:AH6"/>
+    <mergeCell ref="B29:AH31"/>
+    <mergeCell ref="B15:AH15"/>
+    <mergeCell ref="B38:AH40"/>
+    <mergeCell ref="B32:AH34"/>
+    <mergeCell ref="A22:AH22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>患者満足度アンケート集計表（2月）</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>回収率：</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>患者</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年代</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>看護師の対応で気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
+      <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8">
+        <f>SUM(C7:AG7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8">
+        <f>SUM(C8:AG8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>看護師の服装や身だしなみで気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="8" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8">
+        <f>SUM(C10:AG10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
+      <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8">
+        <f>SUM(C11:AG11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ナースコールは迅速に対応できましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
+      <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8">
+        <f>SUM(C13:AG13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8">
+        <f>SUM(C14:AG14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>病室内の環境で不快な点はありましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="8" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8">
+        <f>SUM(C16:AG16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="8" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="8" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
+      <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8">
+        <f>SUM(C17:AG17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>病室内は整理整頓されていましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="8" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="8" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
+      <c r="AE19" s="8" t="n"/>
+      <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8">
+        <f>SUM(C19:AG19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="8" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="8" t="n"/>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="8" t="n"/>
+      <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8">
+        <f>SUM(C20:AG20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>自由記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B23:AH25"/>
+    <mergeCell ref="B18:AH18"/>
+    <mergeCell ref="B9:AH9"/>
+    <mergeCell ref="B26:AH28"/>
+    <mergeCell ref="B12:AH12"/>
+    <mergeCell ref="B35:AH37"/>
+    <mergeCell ref="B6:AH6"/>
+    <mergeCell ref="B29:AH31"/>
+    <mergeCell ref="B15:AH15"/>
+    <mergeCell ref="B38:AH40"/>
+    <mergeCell ref="B32:AH34"/>
+    <mergeCell ref="A22:AH22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>患者満足度アンケート集計表（3月）</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>回収率：</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>患者</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年代</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>看護師の対応で気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
+      <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8">
+        <f>SUM(C7:AG7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8">
+        <f>SUM(C8:AG8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>看護師の服装や身だしなみで気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="8" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8">
+        <f>SUM(C10:AG10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
+      <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8">
+        <f>SUM(C11:AG11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ナースコールは迅速に対応できましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
+      <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8">
+        <f>SUM(C13:AG13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8">
+        <f>SUM(C14:AG14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>病室内の環境で不快な点はありましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="8" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8">
+        <f>SUM(C16:AG16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="8" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="8" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
+      <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8">
+        <f>SUM(C17:AG17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>病室内は整理整頓されていましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="8" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="8" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
+      <c r="AE19" s="8" t="n"/>
+      <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8">
+        <f>SUM(C19:AG19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="8" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="8" t="n"/>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="8" t="n"/>
+      <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8">
+        <f>SUM(C20:AG20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>自由記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B23:AH25"/>
+    <mergeCell ref="B18:AH18"/>
+    <mergeCell ref="B9:AH9"/>
+    <mergeCell ref="B26:AH28"/>
+    <mergeCell ref="B12:AH12"/>
+    <mergeCell ref="B35:AH37"/>
+    <mergeCell ref="B6:AH6"/>
+    <mergeCell ref="B29:AH31"/>
+    <mergeCell ref="B15:AH15"/>
+    <mergeCell ref="B38:AH40"/>
+    <mergeCell ref="B32:AH34"/>
+    <mergeCell ref="A22:AH22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>患者満足度アンケート集計表（5月）</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>回収率：</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>患者</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年代</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>看護師の対応で気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
+      <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8">
+        <f>SUM(C7:AG7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8">
+        <f>SUM(C8:AG8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>看護師の服装や身だしなみで気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="8" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8">
+        <f>SUM(C10:AG10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
+      <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8">
+        <f>SUM(C11:AG11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ナースコールは迅速に対応できましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
+      <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8">
+        <f>SUM(C13:AG13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8">
+        <f>SUM(C14:AG14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>病室内の環境で不快な点はありましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="8" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8">
+        <f>SUM(C16:AG16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="8" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="8" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
+      <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8">
+        <f>SUM(C17:AG17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>病室内は整理整頓されていましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="8" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="8" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
+      <c r="AE19" s="8" t="n"/>
+      <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8">
+        <f>SUM(C19:AG19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="8" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="8" t="n"/>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="8" t="n"/>
+      <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8">
+        <f>SUM(C20:AG20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>自由記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B23:AH25"/>
+    <mergeCell ref="B18:AH18"/>
+    <mergeCell ref="B9:AH9"/>
+    <mergeCell ref="B26:AH28"/>
+    <mergeCell ref="B12:AH12"/>
+    <mergeCell ref="B35:AH37"/>
+    <mergeCell ref="B6:AH6"/>
+    <mergeCell ref="B29:AH31"/>
+    <mergeCell ref="B15:AH15"/>
+    <mergeCell ref="B38:AH40"/>
+    <mergeCell ref="B32:AH34"/>
+    <mergeCell ref="A22:AH22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>患者満足度アンケート集計表（6月）</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>回収率：</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>患者</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年代</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>看護師の対応で気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
+      <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8">
+        <f>SUM(C7:AG7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8">
+        <f>SUM(C8:AG8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>看護師の服装や身だしなみで気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="8" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8">
+        <f>SUM(C10:AG10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
+      <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8">
+        <f>SUM(C11:AG11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ナースコールは迅速に対応できましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
+      <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8">
+        <f>SUM(C13:AG13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8">
+        <f>SUM(C14:AG14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>病室内の環境で不快な点はありましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="8" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8">
+        <f>SUM(C16:AG16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="8" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="8" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
+      <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8">
+        <f>SUM(C17:AG17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>病室内は整理整頓されていましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="8" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="8" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
+      <c r="AE19" s="8" t="n"/>
+      <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8">
+        <f>SUM(C19:AG19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="8" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="8" t="n"/>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="8" t="n"/>
+      <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8">
+        <f>SUM(C20:AG20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>自由記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B23:AH25"/>
+    <mergeCell ref="B18:AH18"/>
+    <mergeCell ref="B9:AH9"/>
+    <mergeCell ref="B26:AH28"/>
+    <mergeCell ref="B12:AH12"/>
+    <mergeCell ref="B35:AH37"/>
+    <mergeCell ref="B6:AH6"/>
+    <mergeCell ref="B29:AH31"/>
+    <mergeCell ref="B15:AH15"/>
+    <mergeCell ref="B38:AH40"/>
+    <mergeCell ref="B32:AH34"/>
+    <mergeCell ref="A22:AH22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>患者満足度アンケート集計表（7月）</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>回収率：</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>患者</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年代</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>看護師の対応で気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
+      <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8">
+        <f>SUM(C7:AG7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8">
+        <f>SUM(C8:AG8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>看護師の服装や身だしなみで気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="8" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8">
+        <f>SUM(C10:AG10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
+      <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8">
+        <f>SUM(C11:AG11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ナースコールは迅速に対応できましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
+      <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8">
+        <f>SUM(C13:AG13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8">
+        <f>SUM(C14:AG14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>病室内の環境で不快な点はありましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="8" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8">
+        <f>SUM(C16:AG16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="8" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="8" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
+      <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8">
+        <f>SUM(C17:AG17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>病室内は整理整頓されていましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="8" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="8" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
+      <c r="AE19" s="8" t="n"/>
+      <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8">
+        <f>SUM(C19:AG19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="8" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="8" t="n"/>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="8" t="n"/>
+      <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8">
+        <f>SUM(C20:AG20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>自由記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B23:AH25"/>
+    <mergeCell ref="B18:AH18"/>
+    <mergeCell ref="B9:AH9"/>
+    <mergeCell ref="B26:AH28"/>
+    <mergeCell ref="B12:AH12"/>
+    <mergeCell ref="B35:AH37"/>
+    <mergeCell ref="B6:AH6"/>
+    <mergeCell ref="B29:AH31"/>
+    <mergeCell ref="B15:AH15"/>
+    <mergeCell ref="B38:AH40"/>
+    <mergeCell ref="B32:AH34"/>
+    <mergeCell ref="A22:AH22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>患者満足度アンケート集計表（8月）</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>回収率：</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>患者</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年代</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>看護師の対応で気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
+      <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8">
+        <f>SUM(C7:AG7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8">
+        <f>SUM(C8:AG8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>看護師の服装や身だしなみで気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="8" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8">
+        <f>SUM(C10:AG10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
+      <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8">
+        <f>SUM(C11:AG11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ナースコールは迅速に対応できましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
+      <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8">
+        <f>SUM(C13:AG13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8">
+        <f>SUM(C14:AG14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>病室内の環境で不快な点はありましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="8" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8">
+        <f>SUM(C16:AG16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="8" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="8" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
+      <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8">
+        <f>SUM(C17:AG17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>病室内は整理整頓されていましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="8" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="8" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
+      <c r="AE19" s="8" t="n"/>
+      <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8">
+        <f>SUM(C19:AG19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="8" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="8" t="n"/>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="8" t="n"/>
+      <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8">
+        <f>SUM(C20:AG20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>自由記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B23:AH25"/>
+    <mergeCell ref="B18:AH18"/>
+    <mergeCell ref="B9:AH9"/>
+    <mergeCell ref="B26:AH28"/>
+    <mergeCell ref="B12:AH12"/>
+    <mergeCell ref="B35:AH37"/>
+    <mergeCell ref="B6:AH6"/>
+    <mergeCell ref="B29:AH31"/>
+    <mergeCell ref="B15:AH15"/>
+    <mergeCell ref="B38:AH40"/>
+    <mergeCell ref="B32:AH34"/>
+    <mergeCell ref="A22:AH22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>患者満足度アンケート集計表（9月）</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>回収率：</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>患者</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年代</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>看護師の対応で気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
+      <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8">
+        <f>SUM(C7:AG7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8">
+        <f>SUM(C8:AG8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>看護師の服装や身だしなみで気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="8" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8">
+        <f>SUM(C10:AG10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
+      <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8">
+        <f>SUM(C11:AG11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ナースコールは迅速に対応できましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
+      <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8">
+        <f>SUM(C13:AG13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8">
+        <f>SUM(C14:AG14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>病室内の環境で不快な点はありましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="8" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8">
+        <f>SUM(C16:AG16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="8" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="8" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
+      <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8">
+        <f>SUM(C17:AG17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>病室内は整理整頓されていましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="8" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="8" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
+      <c r="AE19" s="8" t="n"/>
+      <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8">
+        <f>SUM(C19:AG19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="8" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="8" t="n"/>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="8" t="n"/>
+      <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8">
+        <f>SUM(C20:AG20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>自由記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B23:AH25"/>
+    <mergeCell ref="B18:AH18"/>
+    <mergeCell ref="B9:AH9"/>
+    <mergeCell ref="B26:AH28"/>
+    <mergeCell ref="B12:AH12"/>
+    <mergeCell ref="B35:AH37"/>
+    <mergeCell ref="B6:AH6"/>
+    <mergeCell ref="B29:AH31"/>
+    <mergeCell ref="B15:AH15"/>
+    <mergeCell ref="B38:AH40"/>
+    <mergeCell ref="B32:AH34"/>
+    <mergeCell ref="A22:AH22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>患者満足度アンケート集計表（10月）</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>回収率：</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>患者</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年代</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>看護師の対応で気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
+      <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8">
+        <f>SUM(C7:AG7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8">
+        <f>SUM(C8:AG8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>看護師の服装や身だしなみで気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="8" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8">
+        <f>SUM(C10:AG10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
+      <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8">
+        <f>SUM(C11:AG11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ナースコールは迅速に対応できましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
+      <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8">
+        <f>SUM(C13:AG13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8">
+        <f>SUM(C14:AG14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>病室内の環境で不快な点はありましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="8" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8">
+        <f>SUM(C16:AG16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="8" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="8" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
+      <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8">
+        <f>SUM(C17:AG17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>病室内は整理整頓されていましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="8" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="8" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
+      <c r="AE19" s="8" t="n"/>
+      <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8">
+        <f>SUM(C19:AG19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="8" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="8" t="n"/>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="8" t="n"/>
+      <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8">
+        <f>SUM(C20:AG20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>自由記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B23:AH25"/>
+    <mergeCell ref="B18:AH18"/>
+    <mergeCell ref="B9:AH9"/>
+    <mergeCell ref="B26:AH28"/>
+    <mergeCell ref="B12:AH12"/>
+    <mergeCell ref="B35:AH37"/>
+    <mergeCell ref="B6:AH6"/>
+    <mergeCell ref="B29:AH31"/>
+    <mergeCell ref="B15:AH15"/>
+    <mergeCell ref="B38:AH40"/>
+    <mergeCell ref="B32:AH34"/>
+    <mergeCell ref="A22:AH22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>患者満足度アンケート集計表（11月）</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>回収率：</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>患者</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年代</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>看護師の対応で気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
+      <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8">
+        <f>SUM(C7:AG7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8">
+        <f>SUM(C8:AG8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>看護師の服装や身だしなみで気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="8" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8">
+        <f>SUM(C10:AG10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
+      <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8">
+        <f>SUM(C11:AG11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ナースコールは迅速に対応できましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
+      <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8">
+        <f>SUM(C13:AG13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8">
+        <f>SUM(C14:AG14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>病室内の環境で不快な点はありましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="8" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8">
+        <f>SUM(C16:AG16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="8" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="8" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
+      <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8">
+        <f>SUM(C17:AG17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>病室内は整理整頓されていましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="8" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="8" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
+      <c r="AE19" s="8" t="n"/>
+      <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8">
+        <f>SUM(C19:AG19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="8" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="8" t="n"/>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="8" t="n"/>
+      <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8">
+        <f>SUM(C20:AG20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>自由記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B23:AH25"/>
+    <mergeCell ref="B18:AH18"/>
+    <mergeCell ref="B9:AH9"/>
+    <mergeCell ref="B26:AH28"/>
+    <mergeCell ref="B12:AH12"/>
+    <mergeCell ref="B35:AH37"/>
+    <mergeCell ref="B6:AH6"/>
+    <mergeCell ref="B29:AH31"/>
+    <mergeCell ref="B15:AH15"/>
+    <mergeCell ref="B38:AH40"/>
+    <mergeCell ref="B32:AH34"/>
+    <mergeCell ref="A22:AH22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="8" customWidth="1" min="34" max="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>患者満足度アンケート集計表（12月）</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>回収率：</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>患者</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>年代</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+      <c r="Y5" s="5" t="n"/>
+      <c r="Z5" s="5" t="n"/>
+      <c r="AA5" s="5" t="n"/>
+      <c r="AB5" s="5" t="n"/>
+      <c r="AC5" s="5" t="n"/>
+      <c r="AD5" s="5" t="n"/>
+      <c r="AE5" s="5" t="n"/>
+      <c r="AF5" s="5" t="n"/>
+      <c r="AG5" s="5" t="n"/>
+      <c r="AH5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>看護師の対応で気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="8" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="8" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="n"/>
+      <c r="AD7" s="8" t="n"/>
+      <c r="AE7" s="8" t="n"/>
+      <c r="AF7" s="8" t="n"/>
+      <c r="AG7" s="8" t="n"/>
+      <c r="AH7" s="8">
+        <f>SUM(C7:AG7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="8" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="8" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="8" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="8" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+      <c r="AB8" s="8" t="n"/>
+      <c r="AC8" s="8" t="n"/>
+      <c r="AD8" s="8" t="n"/>
+      <c r="AE8" s="8" t="n"/>
+      <c r="AF8" s="8" t="n"/>
+      <c r="AG8" s="8" t="n"/>
+      <c r="AH8" s="8">
+        <f>SUM(C8:AG8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>看護師の服装や身だしなみで気になった点はありますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="8" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="8" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="8" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="8" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="8" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="8" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+      <c r="AB10" s="8" t="n"/>
+      <c r="AC10" s="8" t="n"/>
+      <c r="AD10" s="8" t="n"/>
+      <c r="AE10" s="8" t="n"/>
+      <c r="AF10" s="8" t="n"/>
+      <c r="AG10" s="8" t="n"/>
+      <c r="AH10" s="8">
+        <f>SUM(C10:AG10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
+      <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8">
+        <f>SUM(C11:AG11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ナースコールは迅速に対応できましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
+      <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
+      <c r="AH13" s="8">
+        <f>SUM(C13:AG13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="8" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="8" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="8" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="8" t="n"/>
+      <c r="AC14" s="8" t="n"/>
+      <c r="AD14" s="8" t="n"/>
+      <c r="AE14" s="8" t="n"/>
+      <c r="AF14" s="8" t="n"/>
+      <c r="AG14" s="8" t="n"/>
+      <c r="AH14" s="8">
+        <f>SUM(C14:AG14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>病室内の環境で不快な点はありましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="8" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="8" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8">
+        <f>SUM(C16:AG16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="8" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="8" t="n"/>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="8" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="8" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="8" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+      <c r="AB17" s="8" t="n"/>
+      <c r="AC17" s="8" t="n"/>
+      <c r="AD17" s="8" t="n"/>
+      <c r="AE17" s="8" t="n"/>
+      <c r="AF17" s="8" t="n"/>
+      <c r="AG17" s="8" t="n"/>
+      <c r="AH17" s="8">
+        <f>SUM(C17:AG17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>病室内は整理整頓されていましたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="8" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="8" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="8" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="8" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="8" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+      <c r="AB19" s="8" t="n"/>
+      <c r="AC19" s="8" t="n"/>
+      <c r="AD19" s="8" t="n"/>
+      <c r="AE19" s="8" t="n"/>
+      <c r="AF19" s="8" t="n"/>
+      <c r="AG19" s="8" t="n"/>
+      <c r="AH19" s="8">
+        <f>SUM(C19:AG19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>いいえ</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="8" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="8" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="8" t="n"/>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="8" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+      <c r="AB20" s="8" t="n"/>
+      <c r="AC20" s="8" t="n"/>
+      <c r="AD20" s="8" t="n"/>
+      <c r="AE20" s="8" t="n"/>
+      <c r="AF20" s="8" t="n"/>
+      <c r="AG20" s="8" t="n"/>
+      <c r="AH20" s="8">
+        <f>SUM(C20:AG20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>自由記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B23:AH25"/>
+    <mergeCell ref="B18:AH18"/>
+    <mergeCell ref="B9:AH9"/>
+    <mergeCell ref="B26:AH28"/>
+    <mergeCell ref="B12:AH12"/>
+    <mergeCell ref="B35:AH37"/>
+    <mergeCell ref="B6:AH6"/>
+    <mergeCell ref="B29:AH31"/>
+    <mergeCell ref="B15:AH15"/>
+    <mergeCell ref="B38:AH40"/>
+    <mergeCell ref="B32:AH34"/>
+    <mergeCell ref="A22:AH22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/患者満足度アンケート集計表.xlsx
+++ b/患者満足度アンケート集計表.xlsx
@@ -514,7 +514,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>患者満足度アンケート集計表（4月）</t>
+          <t>2026年患者満足度アンケート集計表（4月）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1320,7 +1320,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>患者満足度アンケート集計表（1月）</t>
+          <t>2026年患者満足度アンケート集計表（1月）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2126,7 +2126,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>患者満足度アンケート集計表（2月）</t>
+          <t>2026年患者満足度アンケート集計表（2月）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2932,7 +2932,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>患者満足度アンケート集計表（3月）</t>
+          <t>2026年患者満足度アンケート集計表（3月）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3738,7 +3738,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>患者満足度アンケート集計表（5月）</t>
+          <t>2026年患者満足度アンケート集計表（5月）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -4544,7 +4544,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>患者満足度アンケート集計表（6月）</t>
+          <t>2026年患者満足度アンケート集計表（6月）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5350,7 +5350,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>患者満足度アンケート集計表（7月）</t>
+          <t>2026年患者満足度アンケート集計表（7月）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -6156,7 +6156,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>患者満足度アンケート集計表（8月）</t>
+          <t>2026年患者満足度アンケート集計表（8月）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -6962,7 +6962,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>患者満足度アンケート集計表（9月）</t>
+          <t>2026年患者満足度アンケート集計表（9月）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7768,7 +7768,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>患者満足度アンケート集計表（10月）</t>
+          <t>2026年患者満足度アンケート集計表（10月）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8574,7 +8574,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>患者満足度アンケート集計表（11月）</t>
+          <t>2026年患者満足度アンケート集計表（11月）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9380,7 +9380,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>患者満足度アンケート集計表（12月）</t>
+          <t>2026年患者満足度アンケート集計表（12月）</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
